--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -642,19 +642,19 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站川周公路康沈路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+          <t>07:20采样：该车到重点站迎春路金松路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>11/20</t>
         </is>
       </c>
     </row>
@@ -761,19 +761,19 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站莱阳路东陆路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±5分钟</t>
+          <t>07:20采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>8/20</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±10分钟</t>
+          <t>07:20采样：该车到重点站丁香路锦绣路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>4/20</t>
         </is>
       </c>
     </row>
@@ -999,22 +999,26 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>07:20采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,17 +1050,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1066,13 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>15/20</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1183,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1229,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1233,7 +1241,7 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±5分钟</t>
+          <t>07:20采样：该车到重点站白桦路明月路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1248,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1277,7 +1285,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -1302,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>4/20</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1413,7 +1421,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1421,24 +1429,24 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -1451,34 +1459,34 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+          <t>07:20采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1502,37 +1510,1449 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>8/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>136分钟</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X9" s="2" t="inlineStr">
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>2/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>138分钟</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站川周公路康沈路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>14/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>123分钟</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站关岳路康达路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>1/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>142分钟</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站关岳路康达路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>16/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站浦东大道东波路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数125分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>4/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>136分钟</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>1/8</t>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>135分钟</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>8/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>133分钟</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数133分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>3/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>4/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A66373D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -642,26 +642,22 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站迎春路金松路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:01采样，终点ETA 50分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -669,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,17 +689,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -713,17 +709,13 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>136.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -761,26 +753,22 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:01采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -788,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -812,12 +800,12 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -837,12 +825,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/20</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -880,26 +868,22 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站丁香路锦绣路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:01采样，终点ETA 36分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -907,7 +891,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -931,12 +915,12 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -956,12 +940,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/20</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -999,19 +983,19 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
+          <t>08:01采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -1026,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1059,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/20</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1175,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1229,19 +1213,19 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站白桦路明月路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
+          <t>08:01采样：该车到重点站沪南路北中路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1256,7 +1240,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,12 +1289,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/20</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1405,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1459,24 +1443,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±11分钟</t>
+          <t>08:01采样：该车到重点站迎春路长柳路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1486,7 +1470,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1510,7 +1494,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
@@ -1535,12 +1519,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/20</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -1578,19 +1562,19 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
+          <t>08:01采样：该车到重点站沪南路高科西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1605,7 +1589,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1654,12 +1638,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/20</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -1697,24 +1681,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±9分钟</t>
+          <t>08:01采样：该车到重点站白桦路明月路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1724,7 +1708,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1773,12 +1757,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/20</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -1816,19 +1800,19 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站川周公路康沈路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+          <t>08:01采样：该车到重点站沪南路华夏西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1843,7 +1827,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,12 +1876,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/20</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -1935,24 +1919,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站关岳路康达路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±7分钟</t>
+          <t>07:40采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1962,7 +1946,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +1995,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/20</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -2054,19 +2038,19 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站关岳路康达路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±5分钟</t>
+          <t>08:01采样：该车到重点站沪南路华夏西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -2081,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,12 +2114,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>16/20</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -2173,19 +2157,19 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站浦东大道东波路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数125分钟，约±5分钟</t>
+          <t>08:01采样：该车到重点站金杨路云山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2200,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2249,12 +2233,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/20</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -2292,19 +2276,19 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±5分钟</t>
+          <t>08:01采样：该车到重点站康沈路秀康路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2319,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2348,7 +2332,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2368,12 +2352,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/20</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2418,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2484,7 +2468,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2522,19 +2506,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±5分钟</t>
+          <t>08:01采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2549,7 +2533,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2578,7 +2562,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2598,12 +2582,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/20</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -2641,19 +2625,19 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数133分钟估算，约±5分钟</t>
+          <t>08:01采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2668,7 +2652,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2697,7 +2681,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2717,12 +2701,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/20</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -2760,24 +2744,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±10分钟</t>
+          <t>08:01采样：该车到重点站川周公路康沈路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2787,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2816,7 +2800,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2836,12 +2820,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/20</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -2849,22 +2833,22 @@
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>沪A66373D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2897,12 +2881,12 @@
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2952,7 +2936,816 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A66373D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>136分钟</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>144分钟</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>12/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>136分钟</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,14 +446,14 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -654,10 +654,14 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:01采样，终点ETA 50分钟</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -748,27 +756,31 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:01采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,12 +812,12 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -825,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -863,7 +875,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -880,10 +892,14 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:01采样，终点ETA 36分钟</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -891,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -915,12 +931,12 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -945,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -978,29 +994,29 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1010,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1034,12 +1050,12 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -1059,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1108,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq29推进至seq40，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1125,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,10 +1149,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置锦绣路花木路 ETA 7分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1154,7 +1186,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1175,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1213,19 +1245,19 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站沪南路北中路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站沪南路御桥路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1240,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1289,12 +1321,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1437,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1443,19 +1475,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站迎春路长柳路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站沪南路北中路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1470,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1519,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1562,24 +1594,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站沪南路高科西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站锦绣路罗山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1589,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1638,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1681,24 +1713,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站白桦路明月路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±6分钟</t>
+          <t>08:18采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1708,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1757,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1800,19 +1832,19 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站沪南路华夏西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站沪南路高科西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1827,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1876,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2038,19 +2070,19 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站沪南路华夏西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站沪南路高科西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -2065,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2114,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -2157,19 +2189,19 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站金杨路云山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站丁香路锦绣路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2184,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2233,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2276,19 +2308,19 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站康沈路秀康路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站沪南路华夏西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2303,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2352,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2468,7 +2500,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2506,19 +2538,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站沪南路华夏西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2533,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2582,12 +2614,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2625,19 +2657,19 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站金杨路云山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2652,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2701,12 +2733,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2744,24 +2776,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站川周公路康沈路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±7分钟</t>
+          <t>08:18采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2771,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2820,12 +2852,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2863,22 +2895,26 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>08:18采样：该车到重点站康沈路秀康路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -2886,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2910,17 +2946,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2930,13 +2966,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2997,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3047,7 +3087,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3125,19 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±5分钟</t>
+          <t>08:18采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -3112,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3141,7 +3181,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3161,12 +3201,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3204,24 +3244,24 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±7分钟</t>
+          <t>08:18采样：该车到重点站川周公路康沈路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3231,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3260,7 +3300,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3280,12 +3320,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3328,14 +3368,14 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±13分钟</t>
+          <t>08:18采样：该车到重点站关岳路康达路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数132分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3350,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3379,7 +3419,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3399,12 +3439,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3515,7 +3555,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3634,7 +3674,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3745,7 +3785,245 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>135分钟</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq29推进至seq40，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq29推进至seq61，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1240,24 +1240,24 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站沪南路御桥路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -1311,22 +1311,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1470,29 +1470,29 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站沪南路北中路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1589,29 +1589,29 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站锦绣路罗山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1713,26 +1713,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:21采样，终点ETA 11分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1740,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1769,7 +1765,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1779,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1827,29 +1823,29 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站沪南路高科西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1859,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1883,12 +1879,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1908,7 +1904,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2070,19 +2066,19 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站沪南路高科西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+          <t>09:21采样：该车到重点站五莲路兰城路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -2097,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2142,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2189,19 +2185,19 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站丁香路锦绣路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±5分钟</t>
+          <t>09:21采样：该车到重点站周东路川周公路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2216,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2261,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2298,36 +2294,32 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq50，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站沪南路华夏西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -2335,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2343,10 +2335,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq38（站名待映射） ETA 6分钟参与校验</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2359,17 +2367,17 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2379,17 +2387,13 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>149.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2538,19 +2542,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站沪南路华夏西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
+          <t>09:21采样：该车到重点站云山路碧云路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2565,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2614,12 +2618,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -2657,19 +2661,19 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站金杨路云山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
+          <t>09:21采样：该车到重点站康沈路秀沿路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2684,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2733,12 +2737,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2776,24 +2780,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±8分钟</t>
+          <t>09:21采样：该车到重点站云山路碧云路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2803,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2852,12 +2856,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2895,24 +2899,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站康沈路秀康路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±15分钟</t>
+          <t>09:21采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2922,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2946,7 +2950,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
@@ -2971,12 +2975,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3125,19 +3129,19 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+          <t>09:21采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -3152,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3201,12 +3205,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3244,24 +3248,24 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站川周公路康沈路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±6分钟</t>
+          <t>09:21采样：该车到重点站锦绣路花木路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3271,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3320,12 +3324,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3363,24 +3367,24 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站关岳路康达路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数132分钟，约±13分钟</t>
+          <t>09:21采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3390,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3439,12 +3443,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3482,22 +3486,26 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>09:21采样：该车到重点站迎春路长柳路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3505,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3529,17 +3537,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3549,13 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3593,24 +3605,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±7分钟</t>
+          <t>09:21采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3620,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3649,7 +3661,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3669,12 +3681,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3712,22 +3724,26 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>09:21采样：该车到重点站金杨路云山路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3735,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3759,17 +3775,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3779,13 +3795,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3823,24 +3843,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±14分钟</t>
+          <t>09:21采样：该车到重点站沪南路华夏西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3850,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3879,7 +3899,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3899,12 +3919,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3942,19 +3962,19 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
+          <t>09:21采样：该车到重点站金杨路金业路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3969,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3998,32 +4018,1087 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>137分钟</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>09:21采样：该车到重点站康沈路秀康路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>09:21采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数119分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>141分钟</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>09:21采样：该车到重点站浦东大道东波路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数129分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>136分钟</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y30" s="2" t="inlineStr">
+      <c r="Y35" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z30" s="2" t="inlineStr">
+      <c r="Z35" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
+      <c r="AA35" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>145.0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr">
-        <is>
-          <t>10/28</t>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>131分钟</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数131分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1708,27 +1708,31 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:21采样，终点ETA 11分钟</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1736,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1760,12 +1764,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1785,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -2061,29 +2065,29 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站五莲路兰城路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2093,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2117,12 +2121,12 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2132,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2185,26 +2189,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站周东路川周公路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:31采样，终点ETA 11分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2251,22 +2251,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq50，推进12站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq55，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2426,27 +2426,31 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2454,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2478,33 +2482,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2537,29 +2545,29 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>163分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站云山路碧云路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2569,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2593,12 +2601,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2608,22 +2616,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -2656,29 +2664,29 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站康沈路秀沿路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2688,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,12 +2720,12 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2727,22 +2735,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2775,29 +2783,29 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站云山路碧云路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2807,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2831,12 +2839,12 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2846,22 +2854,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2899,26 +2907,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>163分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:11采样，终点ETA 13分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -2926,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,7 +2959,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2965,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3013,27 +3017,31 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -3041,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3065,33 +3073,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3124,24 +3136,24 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -3156,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3180,12 +3192,12 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3205,12 +3217,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3248,24 +3260,24 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站锦绣路花木路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±7分钟</t>
+          <t>10:21采样：该车到重点站东葛路东靖路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数6分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3275,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3324,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3367,24 +3379,24 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±12分钟</t>
+          <t>10:21采样：该车到重点站东波路莱阳路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数17分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3394,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3418,7 +3430,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
@@ -3443,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3486,26 +3498,22 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站迎春路长柳路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:21采样，终点ETA 21分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3513,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3537,12 +3545,12 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3562,7 +3570,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3605,24 +3613,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±9分钟</t>
+          <t>10:21采样：该车到重点站五莲路兰城路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3632,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3681,12 +3689,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3724,19 +3732,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站金杨路云山路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±5分钟</t>
+          <t>10:21采样：该车到重点站沪南路御桥路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3751,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3800,12 +3808,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3848,19 +3856,19 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站沪南路华夏西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±13分钟</t>
+          <t>10:21采样：该车到重点站长岛路张杨北路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3870,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3894,7 +3902,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
@@ -3919,7 +3927,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3962,19 +3970,19 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站金杨路金业路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±5分钟</t>
+          <t>10:21采样：该车到重点站沪南路北中路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3989,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4038,12 +4046,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -4081,19 +4089,19 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站康沈路秀康路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±5分钟</t>
+          <t>10:21采样：该车到重点站云山路碧云路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4108,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4157,12 +4165,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4200,19 +4208,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数119分钟，约±5分钟</t>
+          <t>10:21采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -4227,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4276,7 +4284,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4319,24 +4327,24 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站浦东大道东波路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数129分钟，约±8分钟</t>
+          <t>10:21采样：该车到重点站浦建路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4346,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4395,12 +4403,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4549,24 +4557,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±6分钟</t>
+          <t>10:21采样：该车到重点站锦绣路花木路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4576,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4605,7 +4613,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4625,12 +4633,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4779,24 +4787,24 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±7分钟</t>
+          <t>10:21采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4806,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4835,7 +4843,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4855,12 +4863,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4898,24 +4906,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数131分钟估算，约±6分钟</t>
+          <t>10:21采样：该车到重点站金杨路云山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4925,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4954,7 +4962,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -4974,12 +4982,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5017,19 +5025,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+          <t>10:21采样：该车到重点站康沈路秀康路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -5044,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5073,32 +5081,1091 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>142分钟</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>10:21采样：该车到重点站博兴路兰城路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>151.5</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>24/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>135分钟</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>10:21采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>142分钟</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>10:21采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数132分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>10:21采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>23/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="Y45" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>7/28</t>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A66373D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3141,24 +3141,24 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,17 +3207,17 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3255,29 +3255,29 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站东葛路东靖路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数6分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3384,19 +3384,19 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站东波路莱阳路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数17分钟，约±6分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3493,27 +3493,31 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:21采样，终点ETA 21分钟</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3521,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3545,12 +3549,12 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3570,12 +3574,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3608,29 +3612,29 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站五莲路兰城路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3640,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3664,12 +3668,12 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3689,12 +3693,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3727,24 +3731,24 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站沪南路御桥路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3759,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3783,12 +3787,12 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3798,22 +3802,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3846,29 +3850,29 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站长岛路张杨北路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3878,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3902,12 +3906,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3917,22 +3921,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3965,24 +3969,24 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站沪南路北中路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3997,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4021,12 +4025,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4046,7 +4050,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4084,29 +4088,29 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站云山路碧云路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4116,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4140,12 +4144,12 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4165,12 +4169,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4203,29 +4207,29 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4235,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4259,12 +4263,12 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4274,22 +4278,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4322,24 +4326,24 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站浦建路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -4354,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4378,12 +4382,12 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4393,22 +4397,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4436,12 +4440,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq29推进至seq58，推进29站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4469,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4477,10 +4481,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq26映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4498,7 +4518,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4557,19 +4577,19 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站锦绣路花木路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
+          <t>11:20采样：该车到重点站东葛路东靖路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数7分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -4584,7 +4604,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4633,7 +4653,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4787,19 +4807,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+          <t>11:20采样：该车到重点站长岛路张杨北路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -4814,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4863,12 +4883,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4938,7 @@
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站金杨路云山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±5分钟</t>
+          <t>11:20采样：该车到重点站康沈路秀沿路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -4933,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,22 +4992,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5030,14 +5050,14 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站康沈路秀康路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±5分钟</t>
+          <t>11:20采样：该车到重点站金杨路金口路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -5052,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5101,7 +5121,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5144,24 +5164,24 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站博兴路兰城路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±5分钟</t>
+          <t>11:20采样：该车到重点站沪南路御桥路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5171,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5220,12 +5240,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -5263,24 +5283,24 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±10分钟</t>
+          <t>11:20采样：该车到重点站沪南路北中路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5290,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5339,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5382,24 +5402,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数132分钟，约±10分钟</t>
+          <t>11:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5409,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5458,12 +5478,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5501,24 +5521,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±5分钟</t>
+          <t>11:20采样：该车到重点站浦建路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5528,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5577,12 +5597,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5697,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5735,19 +5755,19 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+          <t>11:20采样：该车到重点站丁香路锦绣路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -5762,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5791,7 +5811,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5811,7 +5831,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5854,22 +5874,26 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>11:20采样：该车到重点站沪南路华夏西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -5877,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5901,17 +5925,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5921,17 +5945,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5969,24 +5993,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±11分钟</t>
+          <t>11:20采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数114分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5996,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6020,12 +6044,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6045,12 +6069,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6165,6 +6189,831 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>11:20采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数119分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>144分钟</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>11:20采样：该车到重点站莱阳路东陆路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>23/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>142分钟</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数142分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>138.7</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>133分钟</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数133分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
           <t>12/28</t>
         </is>
       </c>

--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,22 +2251,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2382,18 +2382,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2502,17 +2506,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2626,12 +2630,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2735,22 +2739,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2864,12 +2868,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,12 +2983,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3107,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3217,12 +3221,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3345,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,12 +3459,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3583,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3807,17 +3811,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3926,17 +3930,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,12 +4292,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4407,12 +4411,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4449,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq29推进至seq58，推进29站，达到≥2站确认条件</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq29推进至seq64，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4473,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4539,7 +4543,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4572,24 +4576,24 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站东葛路东靖路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数7分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -4604,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4628,12 +4632,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4653,12 +4657,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4773,7 @@
       <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4802,29 +4806,29 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站长岛路张杨北路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4834,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,12 +4862,12 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4873,22 +4877,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4921,29 +4925,29 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站康沈路秀沿路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4953,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4977,12 +4981,12 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -5002,12 +5006,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5040,24 +5044,24 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站金杨路金口路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -5072,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5096,12 +5100,12 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5121,12 +5125,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5159,29 +5163,29 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站沪南路御桥路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5191,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5215,12 +5219,12 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5240,12 +5244,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -5283,26 +5287,22 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站沪南路北中路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:11采样，终点ETA 6分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5397,29 +5397,29 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5468,22 +5468,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5521,26 +5521,22 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站浦建路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:11采样，终点ETA 18分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5548,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5577,7 +5573,7 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5597,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5635,27 +5631,31 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5687,17 +5687,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5707,17 +5707,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5755,19 +5755,19 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站丁香路锦绣路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±5分钟</t>
+          <t>12:20采样：该车到重点站周东路川周公路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5874,24 +5874,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站沪南路华夏西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±6分钟</t>
+          <t>12:20采样：该车到重点站长岛路张杨北路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5993,24 +5993,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数114分钟，约±8分钟</t>
+          <t>12:20采样：该车到重点站沪南路北中路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6227,24 +6227,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数119分钟，约±10分钟</t>
+          <t>12:20采样：该车到重点站锦绣路罗山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6346,19 +6346,19 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站莱阳路东陆路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±5分钟</t>
+          <t>12:20采样：该车到重点站浦建路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6422,12 +6422,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6465,22 +6465,26 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>12:20采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6488,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6512,17 +6516,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6532,17 +6536,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6580,22 +6584,26 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>12:20采样：该车到重点站白桦路明月路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -6603,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6627,17 +6635,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6647,17 +6655,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -6695,19 +6703,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数142分钟估算，约±5分钟</t>
+          <t>12:20采样：该车到重点站沪南路高科西路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -6722,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6751,7 +6759,7 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6771,12 +6779,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6814,24 +6822,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±8分钟</t>
+          <t>12:20采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数115分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6841,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6870,7 +6878,7 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6890,12 +6898,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6938,14 +6946,14 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数133分钟估算，约±12分钟</t>
+          <t>12:20采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -6960,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6989,32 +6997,738 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y55" s="2" t="inlineStr">
+      <c r="Y56" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z55" s="2" t="inlineStr">
+      <c r="Z56" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
+      <c r="AA56" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB55" s="2" t="inlineStr">
-        <is>
-          <t>140.0</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>12/28</t>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>136.3</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>124分钟</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>133分钟</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数133分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>134.3</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>136分钟</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>136分钟</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>136.7</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2620,22 +2620,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3211,17 +3211,17 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3459,12 +3459,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5648,12 +5648,12 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -5767,7 +5767,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站周东路川周公路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±5分钟</t>
+          <t>12:40采样：该车到重点站康弘路康丽路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数3分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5874,26 +5874,22 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站长岛路张杨北路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:31采样，终点ETA 25分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -5901,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5925,12 +5921,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5950,12 +5946,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5989,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -6005,7 +6001,7 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站沪南路北中路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+          <t>12:40采样：该车到重点站康沈路秀沿路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -6020,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6074,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6227,19 +6223,19 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站锦绣路罗山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>12:40采样：该车到重点站长岛路张杨北路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -6254,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6293,17 +6289,17 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6346,19 +6342,19 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站浦建路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
+          <t>12:40采样：该车到重点站沪南路御桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -6373,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6422,12 +6418,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6477,7 +6473,7 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
+          <t>12:40采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -6492,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6584,19 +6580,19 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站白桦路明月路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+          <t>12:40采样：该车到重点站沪南路北中路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -6611,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6660,7 +6656,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6703,19 +6699,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站沪南路高科西路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±5分钟</t>
+          <t>12:40采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -6730,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6779,12 +6775,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6834,12 +6830,12 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数115分钟，约±5分钟</t>
+          <t>12:40采样：该车到重点站金杨路云山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6849,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6941,19 +6937,19 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±12分钟</t>
+          <t>12:40采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -6968,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7017,12 +7013,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7060,24 +7056,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±12分钟</t>
+          <t>12:40采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7087,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7116,7 +7112,7 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7136,12 +7132,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7290,24 +7286,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±5分钟</t>
+          <t>12:40采样：该车到重点站关岳路康达路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7317,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7346,7 +7342,7 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7366,7 +7362,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7436,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7555,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7609,7 +7605,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7723,12 +7719,250 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>138分钟</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>142.7</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>136分钟</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>135.7</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3097,17 +3097,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3459,12 +3459,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3806,22 +3806,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5869,27 +5869,31 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:31采样，终点ETA 25分钟</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -5897,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,12 +5925,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5946,12 +5950,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5984,24 +5988,24 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站康沈路秀沿路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -6016,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6040,12 +6044,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6055,12 +6059,12 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -6108,19 +6112,19 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：12:51采样，终点ETA 9分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
@@ -6131,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6155,17 +6159,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6175,17 +6179,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6223,26 +6227,22 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站长岛路张杨北路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:10采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6337,24 +6337,24 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站沪南路御桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6456,29 +6456,29 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6527,22 +6527,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6580,26 +6580,22 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站沪南路北中路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 21分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -6607,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6631,12 +6627,12 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6656,7 +6652,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6699,26 +6695,22 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 40分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6726,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6750,12 +6742,12 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6775,12 +6767,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6818,24 +6810,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站金杨路云山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±7分钟</t>
+          <t>13:20采样：该车到重点站沪南路御桥路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6845,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,7 +6886,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6937,24 +6929,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±12分钟</t>
+          <t>13:20采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6964,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6988,7 +6980,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
@@ -7013,12 +7005,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7056,24 +7048,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±11分钟</t>
+          <t>13:20采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7083,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7107,7 +7099,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
@@ -7132,7 +7124,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7198,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7286,24 +7278,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站关岳路康达路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±7分钟</t>
+          <t>13:20采样：该车到重点站沪南路高科西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7313,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7362,7 +7354,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7405,24 +7397,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数133分钟估算，约±6分钟</t>
+          <t>13:20采样：该车到重点站金杨路金业路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7432,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7461,7 +7453,7 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7481,12 +7473,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7605,7 +7597,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7613,24 +7605,24 @@
       <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7643,34 +7635,34 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±6分钟</t>
+          <t>13:20采样：该车到重点站康沈路秀康路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7684,7 +7676,7 @@
       <c r="T61" s="2" t="inlineStr"/>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
@@ -7694,12 +7686,12 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7719,12 +7711,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7732,24 +7724,24 @@
       <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7762,34 +7754,34 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±14分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±6分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7803,7 +7795,7 @@
       <c r="T62" s="2" t="inlineStr"/>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
@@ -7813,7 +7805,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
@@ -7838,12 +7830,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7851,24 +7843,24 @@
       <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7881,34 +7873,34 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数150分钟估算，约±13分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7922,47 +7914,626 @@
       <c r="T63" s="2" t="inlineStr"/>
       <c r="U63" s="2" t="inlineStr">
         <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
           <t>13:45</t>
         </is>
       </c>
-      <c r="V63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>136分钟</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W63" s="2" t="inlineStr">
+      <c r="W64" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X63" s="2" t="inlineStr">
+      <c r="X64" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y63" s="2" t="inlineStr">
+      <c r="Y64" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z63" s="2" t="inlineStr">
+      <c r="Z64" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
+      <c r="AA64" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>135.7</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr">
-        <is>
-          <t>8/29</t>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>135.3</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>140分钟</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>138.3</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>155.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>155.5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>157.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1951,19 +1951,19 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>07:40采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±8分钟</t>
+          <t>07:40采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>157.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4401,22 +4401,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4996,22 +4996,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,22 +5349,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6473,12 +6473,12 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6537,12 +6537,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6575,12 +6575,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -6592,10 +6592,14 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 21分钟</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -6603,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6627,12 +6631,12 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6690,27 +6694,31 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 40分钟</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6718,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6742,12 +6750,12 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6757,22 +6765,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6805,29 +6813,29 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站沪南路御桥路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6837,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6861,12 +6869,12 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6886,12 +6894,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6924,29 +6932,29 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6956,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6980,12 +6988,12 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -6995,22 +7003,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7043,29 +7051,29 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7075,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7099,12 +7107,12 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7124,12 +7132,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7157,12 +7165,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7190,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7198,10 +7206,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr"/>
-      <c r="S57" s="2" t="inlineStr"/>
-      <c r="T57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq38（站名待映射） ETA 31分钟参与校验</t>
+        </is>
+      </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -7219,7 +7243,7 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7273,29 +7297,29 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>117分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站沪南路高科西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7305,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7329,12 +7353,12 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7344,22 +7368,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7397,19 +7421,19 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站金杨路金业路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±5分钟</t>
+          <t>14:21采样：该车到重点站康沈路秀沿路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -7424,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7473,12 +7497,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7635,24 +7659,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站康沈路秀康路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±13分钟</t>
+          <t>14:21采样：该车到重点站锦绣路罗山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7662,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7686,7 +7710,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
@@ -7711,7 +7735,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7835,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7873,24 +7897,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数150分钟估算，约±13分钟</t>
+          <t>14:21采样：该车到重点站沪南路高科西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7900,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7924,12 +7948,12 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7949,12 +7973,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7992,24 +8016,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±5分钟</t>
+          <t>14:21采样：该车到重点站金杨路云山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8019,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8048,7 +8072,7 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8068,12 +8092,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8111,24 +8135,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±13分钟</t>
+          <t>14:21采样：该车到重点站浦东大道东波路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数129分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8138,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8167,7 +8191,7 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8187,12 +8211,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8230,22 +8254,26 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>14:21采样：该车到重点站关岳路康达路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数149分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8253,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8277,17 +8305,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8297,12 +8325,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>157.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8315,24 +8343,24 @@
       <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8345,22 +8373,26 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8368,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8382,7 +8414,7 @@
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="V67" s="2" t="inlineStr">
@@ -8392,17 +8424,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8412,17 +8444,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8462,7 @@
       <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -8483,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8522,18 +8554,609 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>157.3</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr"/>
-      <c r="AC68" s="2" t="inlineStr">
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
         <is>
           <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>138分钟</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>143分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数143分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC73"/>
+  <dimension ref="A1:AC77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>157.3</t>
+          <t>150.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2858,14 +2858,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>142.0</t>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3330,14 +3330,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>146.0</t>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4049,17 +4049,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>157.3</t>
+          <t>150.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,14 +5821,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>142.0</t>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6537,12 +6537,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7056,12 +7056,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7132,12 +7132,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq56，推进18站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -7433,14 +7433,10 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站康沈路秀沿路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:50采样，终点ETA 9分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7448,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7477,7 +7473,7 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7502,7 +7498,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7617,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7655,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -7671,14 +7667,10 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站锦绣路罗山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：15:21采样，终点ETA 4分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -7686,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7715,7 +7707,7 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7740,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -7773,29 +7765,29 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7805,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7829,12 +7821,12 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7854,12 +7846,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7892,29 +7884,29 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站沪南路高科西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7924,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7948,12 +7940,12 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7973,12 +7965,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8011,29 +8003,29 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站金杨路云山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8043,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8067,12 +8059,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8092,12 +8084,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8135,24 +8127,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站浦东大道东波路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数129分钟，约±11分钟</t>
+          <t>15:21采样：该车到重点站沪南路北中路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8162,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8186,7 +8178,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
@@ -8211,12 +8203,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8254,24 +8246,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>161分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站关岳路康达路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数149分钟，约±13分钟</t>
+          <t>15:21采样：该车到重点站锦绣路罗山路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8281,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8325,17 +8317,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>157.3</t>
+          <t>150.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -8373,24 +8365,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±6分钟</t>
+          <t>15:21采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8400,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8429,7 +8421,7 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8449,12 +8441,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8492,22 +8484,26 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>15:21采样：该车到重点站锦绣路罗山路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8515,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8539,17 +8535,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8559,17 +8555,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>157.3</t>
+          <t>150.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8680,7 +8676,7 @@
       <c r="AB69" s="2" t="inlineStr"/>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -8718,19 +8714,19 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
+          <t>15:21采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -8745,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8774,7 +8770,7 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8794,12 +8790,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8837,19 +8833,19 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±12分钟</t>
+          <t>15:21采样：该车到重点站川周公路康沈路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -8864,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8893,7 +8889,7 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8913,12 +8909,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8979,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9037,7 +9033,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -9045,24 +9041,24 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9075,34 +9071,30 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数143分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9126,37 +9118,501 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>143分钟</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数143分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X73" s="2" t="inlineStr">
+      <c r="X74" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y73" s="2" t="inlineStr">
+      <c r="Y74" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z73" s="2" t="inlineStr">
+      <c r="Z74" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
+      <c r="AA74" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
+      <c r="AB74" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
         </is>
       </c>
-      <c r="AC73" s="2" t="inlineStr">
-        <is>
-          <t>19/29</t>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>143分钟</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数143分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC77"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>150.2</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1311,22 +1311,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2863,17 +2863,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3335,17 +3335,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3449,22 +3449,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3687,22 +3687,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3925,22 +3925,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>124.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>150.2</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4163,22 +4163,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4282,22 +4282,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4647,22 +4647,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4773,7 @@
       <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4877,22 +4877,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5001,17 +5001,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5115,22 +5115,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5826,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6408,22 +6408,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6537,12 +6537,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,22 +6646,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>124.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6884,22 +6884,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7008,17 +7008,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7122,22 +7122,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -7889,24 +7889,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -8020,12 +8020,12 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -8122,29 +8122,29 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站沪南路北中路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -8246,24 +8246,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站锦绣路罗山路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±15分钟</t>
+          <t>16:20采样：该车到重点站东波路莱阳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数17分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>150.2</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -8360,12 +8360,12 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -8377,12 +8377,12 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -8479,29 +8479,29 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站锦绣路罗山路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±15分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>150.2</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
       <c r="AB69" s="2" t="inlineStr"/>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -8714,26 +8714,22 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 52分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8741,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8765,17 +8761,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8785,17 +8781,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -8828,29 +8824,29 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站川周公路康沈路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8860,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8884,12 +8880,12 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8909,12 +8905,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -8957,14 +8953,14 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+          <t>16:20采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -8979,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9008,7 +9004,7 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9028,12 +9024,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9144,7 +9140,7 @@
       <c r="AB73" s="2" t="inlineStr"/>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -9182,19 +9178,19 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数143分钟估算，约±6分钟</t>
+          <t>16:20采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -9209,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9238,7 +9234,7 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9258,12 +9254,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -9301,22 +9297,26 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>16:20采样：该车到重点站金杨路云山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9324,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9348,17 +9348,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9368,17 +9368,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -9386,24 +9386,24 @@
       <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9416,30 +9416,34 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>16:20采样：该车到重点站博兴路兰城路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9463,22 +9467,22 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9488,12 +9492,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9505,7 @@
       <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -9511,7 +9515,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -9531,34 +9535,34 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数143分钟估算，约±5分钟</t>
+          <t>16:20采样：该车到重点站川周公路康沈路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9572,47 +9576,1118 @@
       <c r="T77" s="2" t="inlineStr"/>
       <c r="U77" s="2" t="inlineStr">
         <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>142.7</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>26/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
           <t>16:08</t>
         </is>
       </c>
-      <c r="V77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>141分钟</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站川周公路康沈路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W77" s="2" t="inlineStr">
+      <c r="W78" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X77" s="2" t="inlineStr">
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>23/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站莱阳路东陆路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>2/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>141分钟</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数130分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>136.3</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>16/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y77" s="2" t="inlineStr">
+      <c r="Y81" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z77" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB77" s="2" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr">
-        <is>
-          <t>24/30</t>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>124.7</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>1/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>133.7</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>10/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>136分钟</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>14/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>3/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>140分钟</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>17/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>132.2</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>8/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:AC93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>143.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>132.2</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,17 +2251,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2501,14 +2501,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>134.5</t>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2739,22 +2739,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3211,22 +3211,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3459,12 +3459,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3568,22 +3568,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>124.7</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4044,17 +4044,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>143.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>132.2</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5001,17 +5001,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5354,17 +5354,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5468,17 +5468,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,14 +5702,14 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
           <t>134.5</t>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,22 +6289,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>124.7</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7008,17 +7008,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7132,12 +7132,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>132.2</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7483,17 +7483,17 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7836,22 +7836,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8074,22 +8074,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -8246,24 +8246,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站东波路莱阳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数17分钟，约±7分钟</t>
+          <t>16:40采样：该车到重点站东高路张杨北路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数2分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8312,17 +8312,17 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>143.6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8377,12 +8377,12 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -8484,24 +8484,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>119分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8550,17 +8550,17 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>143.6</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8709,27 +8709,31 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 52分钟</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8737,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8761,17 +8765,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8781,17 +8785,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -8824,31 +8828,27 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:11采样，终点ETA 11分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:33</t>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -8943,29 +8943,29 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8999,12 +8999,12 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -9057,12 +9057,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq45，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9098,10 +9098,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q73" s="2" t="inlineStr"/>
-      <c r="R73" s="2" t="inlineStr"/>
-      <c r="S73" s="2" t="inlineStr"/>
-      <c r="T73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq26映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -9119,7 +9135,7 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9178,26 +9194,22 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:11采样，终点ETA 50分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9205,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9229,17 +9241,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9249,17 +9261,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -9292,29 +9304,29 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站金杨路云山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9324,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9348,12 +9360,12 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9373,12 +9385,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -9428,7 +9440,7 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站博兴路兰城路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±5分钟</t>
+          <t>17:20采样：该车到重点站沪南路北中路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -9443,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9535,24 +9547,24 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站川周公路康沈路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±12分钟</t>
+          <t>17:20采样：该车到重点站锦绣路罗山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9562,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9586,7 +9598,7 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
@@ -9611,12 +9623,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -9654,7 +9666,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -9666,7 +9678,7 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站川周公路康沈路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±5分钟</t>
+          <t>16:30采样：该车到重点站康沈路秀康路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -9681,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9735,7 +9747,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -9773,19 +9785,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站莱阳路东陆路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±5分钟</t>
+          <t>17:20采样：该车到重点站浦建路锦绣路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -9800,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9849,12 +9861,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -9897,19 +9909,19 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数130分钟，约±11分钟</t>
+          <t>17:20采样：该车到重点站锦绣路花木路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9919,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9968,12 +9980,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -10011,19 +10023,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±9分钟</t>
+          <t>17:20采样：该车到重点站沪南路高科西路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -10038,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10067,7 +10079,7 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10087,7 +10099,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>124.7</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10130,19 +10142,19 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±5分钟</t>
+          <t>17:20采样：该车到重点站白桦路明月路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -10157,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10186,7 +10198,7 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
@@ -10206,12 +10218,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -10249,19 +10261,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±6分钟</t>
+          <t>17:20采样：该车到重点站白桦路明月路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -10276,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10305,7 +10317,7 @@
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10325,12 +10337,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -10373,14 +10385,14 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+          <t>17:20采样：该车到重点站沪南路华夏西路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -10395,7 +10407,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10424,7 +10436,7 @@
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10444,12 +10456,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -10487,19 +10499,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±12分钟</t>
+          <t>17:20采样：该车到重点站博兴路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -10514,7 +10526,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10543,7 +10555,7 @@
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10563,12 +10575,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -10606,19 +10618,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±5分钟</t>
+          <t>17:20采样：该车到重点站康沈路秀康路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -10633,7 +10645,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10662,32 +10674,853 @@
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>5/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>140分钟</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>17:20采样：该车到重点站莱阳路东陆路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>25/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>138分钟</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>17:20采样：该车到重点站关岳路康达路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>133.2</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>6/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>11/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>136分钟</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y86" s="2" t="inlineStr">
+      <c r="Y90" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z86" s="2" t="inlineStr">
+      <c r="Z90" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA86" s="2" t="inlineStr">
+      <c r="AA90" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB86" s="2" t="inlineStr">
-        <is>
-          <t>132.2</t>
-        </is>
-      </c>
-      <c r="AC86" s="2" t="inlineStr">
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
         <is>
           <t>8/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>143.6</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>28/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>123分钟</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数123分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>129.8</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>3/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr"/>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>—/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC93"/>
+  <dimension ref="A1:AC95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>28/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>129.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2506,17 +2506,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3459,12 +3459,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>28/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>129.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5354,17 +5354,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5707,17 +5707,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>129.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7132,12 +7132,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7368,22 +7368,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>28/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>28/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -8948,24 +8948,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9014,22 +9014,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq45，推进17站，达到≥2站确认条件</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq53，推进25站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9194,19 +9194,19 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:11采样，终点ETA 50分钟</t>
+          <t>SHMAAS末次终点ETA推算：17:40采样，终点ETA 8分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr"/>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9241,17 +9241,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9261,17 +9261,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9385,12 +9385,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -9428,26 +9428,22 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站沪南路北中路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:40采样，终点ETA 45分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9455,7 +9451,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9479,12 +9475,12 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9504,12 +9500,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -9547,19 +9543,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站锦绣路罗山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
+          <t>17:40采样：该车到重点站长岛路张杨北路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -9574,7 +9570,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9623,12 +9619,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -9785,19 +9781,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站浦建路锦绣路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>17:40采样：该车到重点站沪南路北中路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -9812,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9861,12 +9857,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -9904,24 +9900,24 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站锦绣路花木路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±12分钟</t>
+          <t>17:40采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9931,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9955,7 +9951,7 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
@@ -9980,12 +9976,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -10023,24 +10019,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站沪南路高科西路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±9分钟</t>
+          <t>17:40采样：该车到重点站锦绣路罗山路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10050,7 +10046,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10099,7 +10095,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10142,19 +10138,19 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站白桦路明月路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
+          <t>17:40采样：该车到重点站浦建路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -10169,7 +10165,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10218,12 +10214,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -10261,24 +10257,24 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站白桦路明月路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±6分钟</t>
+          <t>17:40采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10288,7 +10284,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10337,12 +10333,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -10380,19 +10376,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站沪南路华夏西路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±5分钟</t>
+          <t>17:40采样：该车到重点站沪南路高科西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -10407,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10456,7 +10452,7 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>129.2</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10499,24 +10495,24 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站博兴路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±12分钟</t>
+          <t>17:40采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10526,7 +10522,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10550,7 +10546,7 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
@@ -10575,12 +10571,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -10618,19 +10614,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站康沈路秀康路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
+          <t>17:40采样：该车到重点站沪南路华夏西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -10645,7 +10641,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10694,12 +10690,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -10737,7 +10733,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -10749,12 +10745,12 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站莱阳路东陆路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±8分钟</t>
+          <t>17:40采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数113分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10764,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10818,7 +10814,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -10856,24 +10852,24 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站关岳路康达路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±13分钟</t>
+          <t>17:40采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10883,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10932,7 +10928,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10975,22 +10971,26 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>17:40采样：该车到重点站莱阳路东陆路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数125分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10998,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11022,17 +11022,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11042,17 +11042,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -11090,24 +11090,24 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±14分钟</t>
+          <t>17:40采样：该车到重点站川周公路康沈路 ETA 23分钟；叠加该车自身同类时段从该站到终点历史中位数126分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11166,12 +11166,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -11236,7 +11236,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>28/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11524,6 +11524,240 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>5/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A66373D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>4/31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC95"/>
+  <dimension ref="A1:AC100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>143.6</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>129.2</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>132.8</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>131.8</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2620,22 +2620,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3330,22 +3330,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>28/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3459,12 +3459,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3687,22 +3687,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>143.6</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4163,22 +4163,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>129.2</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>132.8</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5234,17 +5234,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>131.8</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>129.2</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7132,12 +7132,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>132.8</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>131.8</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7717,22 +7717,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>143.6</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>143.6</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8895,17 +8895,17 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq53，推进25站，达到≥2站确认条件</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9375,22 +9375,22 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>28/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -9423,27 +9423,31 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:40采样，终点ETA 45分钟</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9451,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9475,12 +9479,12 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9490,22 +9494,22 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -9543,26 +9547,22 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站长岛路张杨北路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 11分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9743,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -9781,26 +9781,22 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站沪南路北中路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 21分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>15:41</t>
@@ -9808,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9832,12 +9828,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9857,12 +9853,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -9900,26 +9896,22 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 27分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -9927,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9951,12 +9943,12 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9976,12 +9968,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -10019,24 +10011,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站锦绣路罗山路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±7分钟</t>
+          <t>18:21采样：该车到重点站长岛路张杨北路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10046,7 +10038,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10095,7 +10087,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10138,19 +10130,19 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站浦建路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站康沈路秀沿路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -10165,7 +10157,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10204,22 +10196,22 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -10257,19 +10249,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站沪南路御桥路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -10284,7 +10276,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10333,12 +10325,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -10376,19 +10368,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站沪南路高科西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站金杨路金口路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -10403,7 +10395,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10452,12 +10444,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>129.2</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10499,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±7分钟</t>
+          <t>18:21采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -10522,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10614,19 +10606,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站沪南路华夏西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站迎春路金松路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -10641,7 +10633,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10690,12 +10682,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>132.8</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -10733,19 +10725,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数113分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -10760,7 +10752,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10809,12 +10801,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -10852,24 +10844,24 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±12分钟</t>
+          <t>18:21采样：该车到重点站锦绣路花木路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10879,7 +10871,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10903,7 +10895,7 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
@@ -10928,7 +10920,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>131.8</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10971,19 +10963,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站莱阳路东陆路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数125分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -10998,7 +10990,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11047,7 +11039,7 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11090,24 +11082,24 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站川周公路康沈路 ETA 23分钟；叠加该车自身同类时段从该站到终点历史中位数126分钟，约±12分钟</t>
+          <t>18:21采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11117,7 +11109,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11141,7 +11133,7 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
@@ -11166,12 +11158,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -11209,24 +11201,24 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±12分钟</t>
+          <t>18:21采样：该车到重点站金杨路金业路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -11236,7 +11228,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11260,12 +11252,12 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
@@ -11285,12 +11277,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>143.6</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -11328,24 +11320,24 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数123分钟估算，约±7分钟</t>
+          <t>18:21采样：该车到重点站康沈路秀康路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11355,7 +11347,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11384,7 +11376,7 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
@@ -11404,12 +11396,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11462,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11558,24 +11550,24 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±6分钟</t>
+          <t>18:21采样：该车到重点站川周公路康沈路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -11585,7 +11577,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11614,7 +11606,7 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
@@ -11634,7 +11626,7 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11700,7 +11692,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11754,7 +11746,602 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>21/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>131分钟</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数131分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>18/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>141分钟</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数141分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>141.3</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>23/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>141分钟</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数141分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>141.8</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>24/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>21:32</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>137分钟</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>16/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC100"/>
+  <dimension ref="A1:AC107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1311,22 +1311,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>132.2</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2511,12 +2511,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2858,22 +2858,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3449,17 +3449,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3925,17 +3925,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4647,22 +4647,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5115,22 +5115,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,22 +5349,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,22 +5821,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6408,17 +6408,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,17 +6646,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7132,12 +7132,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>132.2</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>132.2</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9256,22 +9256,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9390,7 +9390,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9609,22 +9609,22 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9743,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -9793,10 +9793,14 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 21分钟</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>15:41</t>
@@ -9804,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9828,12 +9832,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9843,14 +9847,14 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
           <t>147.0</t>
@@ -9858,7 +9862,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>28/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -9891,27 +9895,31 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 27分钟</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -9919,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9943,12 +9951,12 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9958,17 +9966,17 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10016,21 +10024,17 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站长岛路张杨北路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:41采样，终点ETA 13分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -10038,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10067,7 +10071,7 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10077,17 +10081,17 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10125,12 +10129,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -10142,12 +10146,12 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站康沈路秀沿路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10157,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10181,12 +10185,12 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
@@ -10206,12 +10210,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -10244,24 +10248,24 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站沪南路御桥路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -10276,7 +10280,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10300,12 +10304,12 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10315,22 +10319,22 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -10368,26 +10372,22 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站金杨路金口路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:01采样，终点ETA 13分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10444,12 +10444,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -10482,29 +10482,29 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10538,12 +10538,12 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10553,22 +10553,22 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -10601,29 +10601,29 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站迎春路金松路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10657,12 +10657,12 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10682,12 +10682,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -10720,29 +10720,29 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -10844,26 +10844,22 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站锦绣路花木路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 25分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10871,7 +10867,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10895,12 +10891,12 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10920,12 +10916,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -10963,19 +10959,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±5分钟</t>
+          <t>19:20采样：该车到重点站康弘路康丽路 ETA 35分钟；叠加该车自身同类时段从该站到终点历史中位数4分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -10990,7 +10986,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11039,12 +11035,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -11082,24 +11078,24 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±9分钟</t>
+          <t>19:20采样：该车到重点站长岛路张杨北路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11109,7 +11105,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11158,12 +11154,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -11201,24 +11197,24 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站金杨路金业路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±9分钟</t>
+          <t>19:20采样：该车到重点站沪南路北中路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -11228,7 +11224,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11277,7 +11273,7 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11320,24 +11316,24 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站康沈路秀康路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±10分钟</t>
+          <t>19:20采样：该车到重点站云山路碧云路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11347,7 +11343,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11396,12 +11392,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -11550,24 +11546,24 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站川周公路康沈路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±8分钟</t>
+          <t>19:20采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -11577,7 +11573,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11626,12 +11622,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>132.2</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -11669,22 +11665,26 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>19:20采样：该车到重点站浦建路锦绣路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11716,17 +11716,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11796,12 +11796,12 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±14分钟</t>
+          <t>19:20采样：该车到重点站锦绣路花木路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -11903,19 +11903,19 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数131分钟估算，约±5分钟</t>
+          <t>19:20采样：该车到重点站金杨路云山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
@@ -11979,12 +11979,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -12022,24 +12022,24 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数141分钟估算，约±5分钟</t>
+          <t>19:20采样：该车到重点站沪南路华夏西路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
@@ -12098,12 +12098,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -12141,24 +12141,24 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数141分钟估算，约±5分钟</t>
+          <t>19:20采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数115分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
@@ -12217,12 +12217,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -12230,24 +12230,24 @@
       <c r="A100" s="2" t="inlineStr"/>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -12260,34 +12260,34 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>21:32</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±5分钟</t>
+          <t>19:20采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12301,47 +12301,876 @@
       <c r="T100" s="2" t="inlineStr"/>
       <c r="U100" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>20/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>21:28</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>19:20采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W100" s="2" t="inlineStr">
+      <c r="W101" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X100" s="2" t="inlineStr">
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>137.2</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>15/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>19:20采样：该车到重点站浦东大道东波路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数119分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>135.2</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>9/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>27/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y100" s="2" t="inlineStr">
+      <c r="Y104" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z100" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA100" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB100" s="2" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
-      </c>
-      <c r="AC100" s="2" t="inlineStr">
-        <is>
-          <t>16/31</t>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>130.8</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>1/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>11/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>141.8</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>24/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>135.8</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>12/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC107"/>
+  <dimension ref="A1:AC110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>147.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>29/32</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/32</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>—/32</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>—/32</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>20/32</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>15/32</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>16/32</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>23/32</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/32</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>12/32</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2501,22 +2501,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>22/32</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>24/32</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/32</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/32</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3092,22 +3092,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>3/32</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>132.2</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/32</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>27/32</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3459,12 +3459,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>17/32</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/32</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>19/32</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>9/32</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>2/32</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>147.4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>29/32</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/32</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>—/32</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4773,7 @@
       <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>—/32</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>20/32</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>15/32</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>16/32</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>23/32</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>12/32</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>24/32</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,22 +5702,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>22/32</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/32</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/32</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6174,22 +6174,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>3/32</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>132.2</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/32</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>17/32</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>9/32</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>2/32</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/32</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>15/32</t>
         </is>
       </c>
     </row>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>20/32</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>—/32</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/32</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>24/32</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/32</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>132.2</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/32</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>9/32</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>147.4</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>29/32</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/32</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>147.4</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>29/32</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
       <c r="AB69" s="2" t="inlineStr"/>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>—/32</t>
         </is>
       </c>
     </row>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>15/32</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>23/32</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/32</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       <c r="AB73" s="2" t="inlineStr"/>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>—/32</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>12/32</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9385,12 +9385,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>27/32</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>19/32</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/32</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>25/32</t>
         </is>
       </c>
     </row>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9852,17 +9852,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>17/32</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>17/32</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10091,12 +10091,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>2/32</t>
         </is>
       </c>
     </row>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10329,12 +10329,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>16/32</t>
         </is>
       </c>
     </row>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>20/32</t>
         </is>
       </c>
     </row>
@@ -10737,12 +10737,12 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/32</t>
         </is>
       </c>
     </row>
@@ -10839,7 +10839,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -10849,17 +10849,21 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 25分钟</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10867,7 +10871,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10891,12 +10895,12 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10916,12 +10920,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10958,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -10964,19 +10968,19 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站康弘路康丽路 ETA 35分钟；叠加该车自身同类时段从该站到终点历史中位数4分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10986,7 +10990,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11010,12 +11014,12 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11025,22 +11029,22 @@
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA89" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>22/32</t>
         </is>
       </c>
     </row>
@@ -11073,7 +11077,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -11083,19 +11087,19 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站长岛路张杨北路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±8分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11105,7 +11109,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11129,12 +11133,12 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11154,12 +11158,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -11192,29 +11196,29 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站沪南路北中路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -11224,7 +11228,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11248,12 +11252,12 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
@@ -11273,12 +11277,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>147.4</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>29/32</t>
         </is>
       </c>
     </row>
@@ -11311,24 +11315,24 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站云山路碧云路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -11343,7 +11347,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11367,12 +11371,12 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
@@ -11392,12 +11396,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>132.2</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/32</t>
         </is>
       </c>
     </row>
@@ -11508,7 +11512,7 @@
       <c r="AB93" s="2" t="inlineStr"/>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>—/32</t>
         </is>
       </c>
     </row>
@@ -11627,7 +11631,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/32</t>
         </is>
       </c>
     </row>
@@ -11660,29 +11664,29 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站浦建路锦绣路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11692,7 +11696,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11716,12 +11720,12 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
@@ -11731,22 +11735,22 @@
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA95" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>3/32</t>
         </is>
       </c>
     </row>
@@ -11779,29 +11783,29 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站锦绣路花木路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11811,7 +11815,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11835,12 +11839,12 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11860,12 +11864,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>27/32</t>
         </is>
       </c>
     </row>
@@ -11903,19 +11907,19 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站金杨路云山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±5分钟</t>
+          <t>20:21采样：该车到重点站康沈路秀沿路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -11930,7 +11934,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11979,12 +11983,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>24/32</t>
         </is>
       </c>
     </row>
@@ -12022,26 +12026,22 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站沪南路华夏西路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±9分钟</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 40分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12049,7 +12049,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12073,12 +12073,12 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
@@ -12098,12 +12098,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>19/32</t>
         </is>
       </c>
     </row>
@@ -12141,19 +12141,19 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数115分钟，约±6分钟</t>
+          <t>20:21采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12217,12 +12217,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>23/32</t>
         </is>
       </c>
     </row>
@@ -12260,24 +12260,24 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±10分钟</t>
+          <t>20:01采样：该车到重点站丁香路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -12287,7 +12287,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
@@ -12336,12 +12336,12 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>17/32</t>
         </is>
       </c>
     </row>
@@ -12379,19 +12379,19 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±5分钟</t>
+          <t>20:21采样：该车到重点站锦绣路罗山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12455,12 +12455,12 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -12498,24 +12498,24 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站浦东大道东波路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数119分钟，约±7分钟</t>
+          <t>20:21采样：该车到重点站浦建路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12574,12 +12574,12 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>12/32</t>
         </is>
       </c>
     </row>
@@ -12617,22 +12617,26 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>20:21采样：该车到重点站沪南路高科西路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>15:41</t>
@@ -12640,7 +12644,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12664,17 +12668,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12684,17 +12688,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>17/32</t>
         </is>
       </c>
     </row>
@@ -12732,24 +12736,24 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±12分钟</t>
+          <t>20:21采样：该车到重点站迎春路长柳路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -12759,7 +12763,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12783,12 +12787,12 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
@@ -12808,12 +12812,12 @@
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>2/32</t>
         </is>
       </c>
     </row>
@@ -12851,24 +12855,24 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±9分钟</t>
+          <t>20:21采样：该车到重点站沪南路高科西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -12878,7 +12882,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12907,7 +12911,7 @@
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
@@ -12927,12 +12931,12 @@
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -12970,19 +12974,19 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+          <t>20:21采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -12997,7 +13001,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13026,7 +13030,7 @@
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
@@ -13046,12 +13050,12 @@
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/32</t>
         </is>
       </c>
     </row>
@@ -13059,24 +13063,24 @@
       <c r="A107" s="2" t="inlineStr"/>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -13089,19 +13093,19 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>22:12</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±5分钟</t>
+          <t>20:21采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数106分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
@@ -13111,12 +13115,12 @@
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13130,47 +13134,396 @@
       <c r="T107" s="2" t="inlineStr"/>
       <c r="U107" s="2" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>1/32</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
           <t>20:05</t>
         </is>
       </c>
-      <c r="V107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>131分钟</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>20:21采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W107" s="2" t="inlineStr">
+      <c r="W108" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X107" s="2" t="inlineStr">
-        <is>
-          <t>同车历史全程时间</t>
-        </is>
-      </c>
-      <c r="Y107" s="2" t="inlineStr">
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z107" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA107" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB107" s="2" t="inlineStr">
-        <is>
-          <t>135.8</t>
-        </is>
-      </c>
-      <c r="AC107" s="2" t="inlineStr">
-        <is>
-          <t>12/31</t>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>136.8</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>16/32</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr"/>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr"/>
+      <c r="R109" s="2" t="inlineStr"/>
+      <c r="S109" s="2" t="inlineStr"/>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z109" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA109" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB109" s="2" t="inlineStr">
+        <is>
+          <t>139.3</t>
+        </is>
+      </c>
+      <c r="AC109" s="2" t="inlineStr">
+        <is>
+          <t>22/32</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr"/>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>沪A66373D</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr"/>
+      <c r="R110" s="2" t="inlineStr"/>
+      <c r="S110" s="2" t="inlineStr"/>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z110" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA110" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB110" s="2" t="inlineStr">
+        <is>
+          <t>130.7</t>
+        </is>
+      </c>
+      <c r="AC110" s="2" t="inlineStr">
+        <is>
+          <t>3/32</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>14/32</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/32</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>5/32</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>20/32</t>
+          <t>19/32</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/32</t>
+          <t>17/32</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/32</t>
+          <t>12/32</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>20/32</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/32</t>
+          <t>15/32</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>15/32</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2506,17 +2506,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>22/32</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>24/32</t>
+          <t>25/32</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>9/32</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>26/32</t>
+          <t>23/32</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3097,17 +3097,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/32</t>
+          <t>2/32</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3454,17 +3454,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/32</t>
+          <t>22/32</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>19/32</t>
+          <t>18/32</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/32</t>
+          <t>10/32</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3930,17 +3930,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/32</t>
+          <t>3/32</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>14/32</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/32</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>5/32</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>20/32</t>
+          <t>19/32</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/32</t>
+          <t>17/32</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/32</t>
+          <t>12/32</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>20/32</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/32</t>
+          <t>15/32</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>24/32</t>
+          <t>25/32</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5707,17 +5707,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>22/32</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>26/32</t>
+          <t>23/32</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>9/32</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6179,17 +6179,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/32</t>
+          <t>2/32</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6413,17 +6413,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>17/32</t>
+          <t>22/32</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/32</t>
+          <t>10/32</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6651,17 +6651,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/32</t>
+          <t>3/32</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/32</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/32</t>
+          <t>17/32</t>
         </is>
       </c>
     </row>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>20/32</t>
+          <t>19/32</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>15/32</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>24/32</t>
+          <t>25/32</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>9/32</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/32</t>
+          <t>10/32</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>15/32</t>
+          <t>17/32</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>20/32</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>12/32</t>
+          <t>15/32</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>19/32</t>
+          <t>18/32</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>26/32</t>
+          <t>23/32</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>17/32</t>
+          <t>23/32</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9971,17 +9971,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>17/32</t>
+          <t>22/32</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10086,17 +10086,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>2/32</t>
+          <t>3/32</t>
         </is>
       </c>
     </row>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>14/32</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10329,12 +10329,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>5/32</t>
         </is>
       </c>
     </row>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/32</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>16/32</t>
+          <t>12/32</t>
         </is>
       </c>
     </row>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>20/32</t>
+          <t>19/32</t>
         </is>
       </c>
     </row>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>11/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -10990,7 +10990,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11034,17 +11034,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>22/32</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>9/32</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11740,17 +11740,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>3/32</t>
+          <t>2/32</t>
         </is>
       </c>
     </row>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11902,29 +11902,29 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站康沈路秀沿路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
@@ -11983,12 +11983,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>24/32</t>
+          <t>25/32</t>
         </is>
       </c>
     </row>
@@ -12021,27 +12021,31 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 40分钟</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12049,7 +12053,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12073,12 +12077,12 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
@@ -12098,12 +12102,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>19/32</t>
+          <t>18/32</t>
         </is>
       </c>
     </row>
@@ -12136,29 +12140,29 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12168,7 +12172,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12192,12 +12196,12 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
@@ -12217,12 +12221,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>20/32</t>
         </is>
       </c>
     </row>
@@ -12250,36 +12254,32 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq64，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>20:01采样：该车到重点站丁香路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -12287,7 +12287,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12295,10 +12295,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="inlineStr"/>
-      <c r="R100" s="2" t="inlineStr"/>
-      <c r="S100" s="2" t="inlineStr"/>
-      <c r="T100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12311,17 +12327,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12331,17 +12347,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>17/32</t>
+          <t>22/32</t>
         </is>
       </c>
     </row>
@@ -12374,29 +12390,29 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站锦绣路罗山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -12406,7 +12422,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12430,12 +12446,12 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
@@ -12455,12 +12471,12 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>14/32</t>
         </is>
       </c>
     </row>
@@ -12493,29 +12509,29 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站浦建路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -12525,7 +12541,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12549,12 +12565,12 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
@@ -12574,12 +12590,12 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>12/32</t>
+          <t>15/32</t>
         </is>
       </c>
     </row>
@@ -12617,19 +12633,19 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站沪南路高科西路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
+          <t>20:51采样：该车到重点站云山路碧云路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -12644,7 +12660,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12693,12 +12709,12 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>17/32</t>
+          <t>23/32</t>
         </is>
       </c>
     </row>
@@ -12726,36 +12742,32 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站迎春路长柳路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -12763,7 +12775,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12771,10 +12783,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q104" s="2" t="inlineStr"/>
-      <c r="R104" s="2" t="inlineStr"/>
-      <c r="S104" s="2" t="inlineStr"/>
-      <c r="T104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±3分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12787,17 +12815,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12807,17 +12835,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>2/32</t>
+          <t>3/32</t>
         </is>
       </c>
     </row>
@@ -12855,19 +12883,19 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>21:44</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站沪南路高科西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±5分钟</t>
+          <t>21:20采样：该车到重点站东波路莱阳路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -12882,7 +12910,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12931,12 +12959,12 @@
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>5/32</t>
         </is>
       </c>
     </row>
@@ -12969,29 +12997,29 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -13001,7 +13029,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13025,12 +13053,12 @@
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
@@ -13050,12 +13078,12 @@
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>26/32</t>
+          <t>23/32</t>
         </is>
       </c>
     </row>
@@ -13093,19 +13121,19 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>22:08</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数106分钟，约±5分钟</t>
+          <t>21:20采样：该车到重点站沪南路御桥路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
@@ -13120,7 +13148,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13169,7 +13197,7 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
@@ -13212,19 +13240,19 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
+          <t>21:20采样：该车到重点站云山路碧云路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
@@ -13239,7 +13267,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13288,12 +13316,12 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>16/32</t>
+          <t>12/32</t>
         </is>
       </c>
     </row>
@@ -13331,22 +13359,26 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:24</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>115分钟</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="inlineStr"/>
+          <t>21:20采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -13354,7 +13386,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -13378,17 +13410,17 @@
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X109" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y109" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z109" s="2" t="inlineStr">
@@ -13398,17 +13430,17 @@
       </c>
       <c r="AA109" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB109" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>22/32</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -13446,22 +13478,26 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:54</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M110" s="2" t="inlineStr"/>
+          <t>21:20采样：该车到重点站康沈路秀康路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -13469,7 +13505,7 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
@@ -13493,17 +13529,17 @@
       </c>
       <c r="W110" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X110" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y110" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z110" s="2" t="inlineStr">
@@ -13513,17 +13549,17 @@
       </c>
       <c r="AA110" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>3/32</t>
+          <t>2/32</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东35路.xlsx
+++ b/data/export/2026-09-20-浦东35路.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/32</t>
+          <t>10/32</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>132.8</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/32</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2511,12 +2511,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/32</t>
+          <t>8/32</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>24/32</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/32</t>
+          <t>9/32</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/32</t>
+          <t>10/32</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>132.8</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/32</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>24/32</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/32</t>
+          <t>8/32</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/32</t>
+          <t>9/32</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/32</t>
+          <t>10/32</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/32</t>
+          <t>8/32</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/32</t>
+          <t>9/32</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/32</t>
+          <t>10/32</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>24/32</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>14/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10329,12 +10329,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>132.8</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>5/32</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>12/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -10990,7 +10990,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11039,12 +11039,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>9/32</t>
+          <t>8/32</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>14/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -12747,7 +12747,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -12775,7 +12775,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12878,29 +12878,29 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>21:41</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站东波路莱阳路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12934,12 +12934,12 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
@@ -12959,12 +12959,12 @@
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>132.8</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>5/32</t>
+          <t>6/32</t>
         </is>
       </c>
     </row>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13078,12 +13078,12 @@
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>24/32</t>
         </is>
       </c>
     </row>
@@ -13116,29 +13116,29 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>22:04</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站沪南路御桥路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13172,12 +13172,12 @@
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X107" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y107" s="2" t="inlineStr">
@@ -13197,7 +13197,7 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
@@ -13235,29 +13235,29 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站云山路碧云路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13291,12 +13291,12 @@
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X108" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y108" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>12/32</t>
+          <t>11/32</t>
         </is>
       </c>
     </row>
@@ -13359,26 +13359,22 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>22:24</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>115分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:51采样，终点ETA 42分钟</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
       <c r="N109" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -13386,7 +13382,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -13410,12 +13406,12 @@
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X109" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y109" s="2" t="inlineStr">
@@ -13435,12 +13431,12 @@
       </c>
       <c r="AB109" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>13/32</t>
         </is>
       </c>
     </row>
@@ -13478,19 +13474,19 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>22:54</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站康沈路秀康路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
+          <t>21:51采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -13505,7 +13501,7 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
@@ -13554,7 +13550,7 @@
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AC110" s="2" t="inlineStr">
